--- a/data/result_20260910_143902 (additional impact acc).xlsx
+++ b/data/result_20260910_143902 (additional impact acc).xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei.kc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei.kc\Desktop\Adhoc\03 Sept 2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:8001_{72606440-8F03-475A-8EFF-F8346883AE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABBE89AE-A81D-468D-8F90-F8A1B54AD494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results export" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="152">
   <si>
     <t>user_id</t>
   </si>
@@ -483,6 +486,12 @@
   </si>
   <si>
     <t>AES_UvWPnIdAILdc9irpEafl9A==</t>
+  </si>
+  <si>
+    <t>ban_reason</t>
+  </si>
+  <si>
+    <t>ban_date</t>
   </si>
 </sst>
 </file>
@@ -535,6 +544,375 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Results export"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="F2" t="str">
+            <v>43374604</v>
+          </cell>
+          <cell r="G2" t="str">
+            <v>FTU đặt hơn 40 đơn phá</v>
+          </cell>
+          <cell r="H2" t="str">
+            <v>2031-08-06 10:06:49</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="F3" t="str">
+            <v>43891958</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v>disruptive user, more than 20 fake orders</v>
+          </cell>
+          <cell r="H3" t="str">
+            <v>2031-08-25 09:35:57</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="F4" t="str">
+            <v>43862968</v>
+          </cell>
+          <cell r="G4" t="str">
+            <v>disruptive user, more than 20 fake orders</v>
+          </cell>
+          <cell r="H4" t="str">
+            <v>2031-08-24 10:23:29</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="F5" t="str">
+            <v>42459099</v>
+          </cell>
+          <cell r="G5" t="str">
+            <v>Fake order - Đặt 49 đơn liên tục, địa chỉ ko chính xác, tài xế không liên hệ được</v>
+          </cell>
+          <cell r="H5" t="str">
+            <v>2031-07-22 10:24:05</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="F6" t="str">
+            <v>42426641</v>
+          </cell>
+          <cell r="G6" t="str">
+            <v>Fake orders - FTU đặt hơn 200 đơn hàng, địa chỉ không cụ thể, các TX đều không liên hệ được</v>
+          </cell>
+          <cell r="H6" t="str">
+            <v>2031-07-22 12:09:47</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="F7" t="str">
+            <v>42406507</v>
+          </cell>
+          <cell r="G7" t="str">
+            <v>Fake orders - FTU đặt hơn 200 đơn hàng, địa chỉ không cụ thể, các TX đều không liên hệ được</v>
+          </cell>
+          <cell r="H7" t="str">
+            <v>2031-07-22 12:10:28</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="F8" t="str">
+            <v>42971568</v>
+          </cell>
+          <cell r="G8" t="str">
+            <v>FTU đặt hơn 100 đơn phá, các TX đến nơi không liên hệ được</v>
+          </cell>
+          <cell r="H8" t="str">
+            <v>2031-07-23 11:30:19</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="F9" t="str">
+            <v>42997602</v>
+          </cell>
+          <cell r="G9" t="str">
+            <v>FTU đặt hơn 200 đơn hàng, địa chỉ không cụ thể, các TX đều không liên hệ được</v>
+          </cell>
+          <cell r="H9" t="str">
+            <v>2031-07-24 10:24:04</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="F10" t="str">
+            <v>43614456</v>
+          </cell>
+          <cell r="G10" t="str">
+            <v>FTU placed over 100 disruptive order</v>
+          </cell>
+          <cell r="H10" t="str">
+            <v>2031-08-15 10:07:41</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="F11" t="str">
+            <v>43674483</v>
+          </cell>
+          <cell r="G11" t="str">
+            <v>disruptive user, more than 20 fake orders</v>
+          </cell>
+          <cell r="H11" t="str">
+            <v>2031-08-17 08:56:05</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="F12" t="str">
+            <v>43430885</v>
+          </cell>
+          <cell r="G12" t="str">
+            <v>FTU placed over 100 disruptive orders</v>
+          </cell>
+          <cell r="H12" t="str">
+            <v>2031-08-10 10:29:23</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="F13" t="str">
+            <v>43230061</v>
+          </cell>
+          <cell r="G13" t="str">
+            <v>FTU đặt hơn 100 đơn phá</v>
+          </cell>
+          <cell r="H13" t="str">
+            <v>2031-08-01 10:01:46</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="F14" t="str">
+            <v>43319297</v>
+          </cell>
+          <cell r="G14" t="str">
+            <v>FTU đặt hơn 100 đơn phá</v>
+          </cell>
+          <cell r="H14" t="str">
+            <v>2031-08-04 10:10:58</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="F15" t="str">
+            <v>43166702</v>
+          </cell>
+          <cell r="G15" t="str">
+            <v>Disruptive user, TX Phạm Minh Truyền 2852976 báo cáo Kh 43166702 đặt phá</v>
+          </cell>
+          <cell r="H15" t="str">
+            <v>2031-07-30 10:00:09</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="F16" t="str">
+            <v>43022614</v>
+          </cell>
+          <cell r="G16" t="str">
+            <v>User đặt hơn 160 đơn phá, các TX đều không liên hệ được</v>
+          </cell>
+          <cell r="H16" t="str">
+            <v>2031-07-27 10:39:43</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="F17" t="str">
+            <v>43978801</v>
+          </cell>
+          <cell r="G17" t="str">
+            <v>Placed more than 80 fake orders</v>
+          </cell>
+          <cell r="H17" t="str">
+            <v>2031-08-28 10:10:00</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="F18" t="str">
+            <v>43290314</v>
+          </cell>
+          <cell r="G18" t="str">
+            <v>FTU đặt hơn 100 đơn phá. Offensive user's name</v>
+          </cell>
+          <cell r="H18" t="str">
+            <v>2031-08-03 10:24:03</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="F19" t="str">
+            <v>42463024</v>
+          </cell>
+          <cell r="G19" t="str">
+            <v>Fake orders. Đặt 61 đơn trong 3 ngày, không liên hệ được</v>
+          </cell>
+          <cell r="H19" t="str">
+            <v>2031-07-22 10:10:28</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="F20" t="str">
+            <v>42913719</v>
+          </cell>
+          <cell r="G20" t="str">
+            <v>Fake order - Corp đặt 200 đơn phá, các TX đều ko liên hệ được</v>
+          </cell>
+          <cell r="H20" t="str">
+            <v>2031-07-22 10:25:04</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="F21" t="str">
+            <v>43539274</v>
+          </cell>
+          <cell r="G21" t="str">
+            <v>FTU placed over 100 disruptive order</v>
+          </cell>
+          <cell r="H21" t="str">
+            <v>2031-08-12 10:27:38</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="F22" t="str">
+            <v>43138108</v>
+          </cell>
+          <cell r="G22" t="str">
+            <v>disruptive user, TX Phạm Minh Truyền 2852976 báo cáo Kh 43138108 đặt phá đơn</v>
+          </cell>
+          <cell r="H22" t="str">
+            <v>2031-07-29 09:27:17</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="F23" t="str">
+            <v>43920615</v>
+          </cell>
+          <cell r="G23" t="str">
+            <v>Placed more than 100 fake orders</v>
+          </cell>
+          <cell r="H23" t="str">
+            <v>2031-08-26 10:16:44</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="F24" t="str">
+            <v>43346700</v>
+          </cell>
+          <cell r="G24" t="str">
+            <v>User đặt hơn 100 đơn phá</v>
+          </cell>
+          <cell r="H24" t="str">
+            <v>2031-08-05 10:13:34</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="F25" t="str">
+            <v>43949404</v>
+          </cell>
+          <cell r="G25" t="str">
+            <v>Placed over 100 fake orders</v>
+          </cell>
+          <cell r="H25" t="str">
+            <v>2031-08-27 11:18:17</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="F26" t="str">
+            <v>43566043</v>
+          </cell>
+          <cell r="G26" t="str">
+            <v>FTU placed over 100 disruptive order</v>
+          </cell>
+          <cell r="H26" t="str">
+            <v>2031-08-13 10:16:23</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="F27" t="str">
+            <v>43110506</v>
+          </cell>
+          <cell r="G27" t="str">
+            <v>disruptive user</v>
+          </cell>
+          <cell r="H27" t="str">
+            <v>2031-07-28 09:56:11</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="F28" t="str">
+            <v>43402439</v>
+          </cell>
+          <cell r="G28" t="str">
+            <v>FTU placed over 100 disruptive orders</v>
+          </cell>
+          <cell r="H28" t="str">
+            <v>2031-08-07 10:35:45</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="F29" t="str">
+            <v>44010401</v>
+          </cell>
+          <cell r="G29" t="str">
+            <v>Placed over 100 fake orders</v>
+          </cell>
+          <cell r="H29" t="str">
+            <v>2031-08-31 10:06:07</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="F30" t="str">
+            <v>43081554</v>
+          </cell>
+          <cell r="G30" t="str">
+            <v>disruptive user, more than 20 fake orders</v>
+          </cell>
+          <cell r="H30" t="str">
+            <v>2031-07-27 09:06:11</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="F31" t="str">
+            <v>42463063</v>
+          </cell>
+          <cell r="G31" t="str">
+            <v>Disruptive user, banning and tagging under Platform Ops and MD approve</v>
+          </cell>
+          <cell r="H31" t="str">
+            <v>2031-07-07 16:34:11</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="F32" t="str">
+            <v>42426592</v>
+          </cell>
+          <cell r="G32" t="str">
+            <v>Fake order - FTU đặt hơn 200 đơn hàng, địa chỉ không cụ thể, các TX đều không liên hệ được</v>
+          </cell>
+          <cell r="H32" t="str">
+            <v>2031-07-22 11:54:57</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="F33" t="str">
+            <v>43593087</v>
+          </cell>
+          <cell r="G33" t="str">
+            <v>disruptive user</v>
+          </cell>
+          <cell r="H33" t="str">
+            <v>2031-08-14 09:43:19</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -854,7 +1232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -864,9 +1242,11 @@
     <col min="5" max="5" width="9.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -888,8 +1268,14 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -911,8 +1297,16 @@
       <c r="G2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2" t="str">
+        <f>_xlfn.XLOOKUP(A2,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>FTU placed over 100 disruptive order</v>
+      </c>
+      <c r="I2" t="str">
+        <f>_xlfn.XLOOKUP(A2,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-12 10:27:38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -934,8 +1328,16 @@
       <c r="G3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3" t="str">
+        <f>_xlfn.XLOOKUP(A3,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>Fake order - FTU đặt hơn 200 đơn hàng, địa chỉ không cụ thể, các TX đều không liên hệ được</v>
+      </c>
+      <c r="I3" t="str">
+        <f>_xlfn.XLOOKUP(A3,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-07-22 11:54:57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -957,8 +1359,16 @@
       <c r="G4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4" t="str">
+        <f>_xlfn.XLOOKUP(A4,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>Placed more than 80 fake orders</v>
+      </c>
+      <c r="I4" t="str">
+        <f>_xlfn.XLOOKUP(A4,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-28 10:10:00</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -980,8 +1390,16 @@
       <c r="G5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5" t="str">
+        <f>_xlfn.XLOOKUP(A5,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>Placed over 100 fake orders</v>
+      </c>
+      <c r="I5" t="str">
+        <f>_xlfn.XLOOKUP(A5,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-31 10:06:07</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1003,8 +1421,16 @@
       <c r="G6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6" t="str">
+        <f>_xlfn.XLOOKUP(A6,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>disruptive user, more than 20 fake orders</v>
+      </c>
+      <c r="I6" t="str">
+        <f>_xlfn.XLOOKUP(A6,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-24 10:23:29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1026,8 +1452,16 @@
       <c r="G7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7" t="str">
+        <f>_xlfn.XLOOKUP(A7,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>disruptive user, more than 20 fake orders</v>
+      </c>
+      <c r="I7" t="str">
+        <f>_xlfn.XLOOKUP(A7,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-25 09:35:57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -1049,8 +1483,16 @@
       <c r="G8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8" t="str">
+        <f>_xlfn.XLOOKUP(A8,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>FTU đặt hơn 100 đơn phá</v>
+      </c>
+      <c r="I8" t="str">
+        <f>_xlfn.XLOOKUP(A8,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-01 10:01:46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -1072,8 +1514,16 @@
       <c r="G9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9" t="str">
+        <f>_xlfn.XLOOKUP(A9,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>disruptive user, more than 20 fake orders</v>
+      </c>
+      <c r="I9" t="str">
+        <f>_xlfn.XLOOKUP(A9,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-07-27 09:06:11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -1095,8 +1545,16 @@
       <c r="G10" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10" t="e">
+        <f>_xlfn.XLOOKUP(A10,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I10" t="e">
+        <f>_xlfn.XLOOKUP(A10,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -1118,8 +1576,16 @@
       <c r="G11" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11" t="str">
+        <f>_xlfn.XLOOKUP(A11,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>Disruptive user, banning and tagging under Platform Ops and MD approve</v>
+      </c>
+      <c r="I11" t="str">
+        <f>_xlfn.XLOOKUP(A11,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-07-07 16:34:11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -1141,8 +1607,16 @@
       <c r="G12" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12" t="str">
+        <f>_xlfn.XLOOKUP(A12,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>User đặt hơn 160 đơn phá, các TX đều không liên hệ được</v>
+      </c>
+      <c r="I12" t="str">
+        <f>_xlfn.XLOOKUP(A12,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-07-27 10:39:43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -1164,8 +1638,16 @@
       <c r="G13" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13" t="str">
+        <f>_xlfn.XLOOKUP(A13,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>Placed more than 100 fake orders</v>
+      </c>
+      <c r="I13" t="str">
+        <f>_xlfn.XLOOKUP(A13,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-26 10:16:44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -1187,8 +1669,16 @@
       <c r="G14" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14" t="e">
+        <f>_xlfn.XLOOKUP(A14,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I14" t="e">
+        <f>_xlfn.XLOOKUP(A14,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>54</v>
       </c>
@@ -1210,8 +1700,16 @@
       <c r="G15" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15" t="str">
+        <f>_xlfn.XLOOKUP(A15,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>Fake orders - FTU đặt hơn 200 đơn hàng, địa chỉ không cụ thể, các TX đều không liên hệ được</v>
+      </c>
+      <c r="I15" t="str">
+        <f>_xlfn.XLOOKUP(A15,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-07-22 12:10:28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>57</v>
       </c>
@@ -1233,8 +1731,16 @@
       <c r="G16" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16" t="e">
+        <f>_xlfn.XLOOKUP(A16,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I16" t="e">
+        <f>_xlfn.XLOOKUP(A16,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>60</v>
       </c>
@@ -1256,8 +1762,16 @@
       <c r="G17" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17" t="str">
+        <f>_xlfn.XLOOKUP(A17,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>User đặt hơn 100 đơn phá</v>
+      </c>
+      <c r="I17" t="str">
+        <f>_xlfn.XLOOKUP(A17,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-05 10:13:34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>63</v>
       </c>
@@ -1279,8 +1793,16 @@
       <c r="G18" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18" t="str">
+        <f>_xlfn.XLOOKUP(A18,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>FTU đặt hơn 100 đơn phá</v>
+      </c>
+      <c r="I18" t="str">
+        <f>_xlfn.XLOOKUP(A18,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-04 10:10:58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>66</v>
       </c>
@@ -1302,8 +1824,16 @@
       <c r="G19" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19" t="str">
+        <f>_xlfn.XLOOKUP(A19,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>Placed over 100 fake orders</v>
+      </c>
+      <c r="I19" t="str">
+        <f>_xlfn.XLOOKUP(A19,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-27 11:18:17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>69</v>
       </c>
@@ -1325,8 +1855,16 @@
       <c r="G20" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20" t="str">
+        <f>_xlfn.XLOOKUP(A20,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>Fake orders - FTU đặt hơn 200 đơn hàng, địa chỉ không cụ thể, các TX đều không liên hệ được</v>
+      </c>
+      <c r="I20" t="str">
+        <f>_xlfn.XLOOKUP(A20,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-07-22 12:09:47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -1348,8 +1886,16 @@
       <c r="G21" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21" t="str">
+        <f>_xlfn.XLOOKUP(A21,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>Fake order - Đặt 49 đơn liên tục, địa chỉ ko chính xác, tài xế không liên hệ được</v>
+      </c>
+      <c r="I21" t="str">
+        <f>_xlfn.XLOOKUP(A21,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-07-22 10:24:05</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>75</v>
       </c>
@@ -1371,8 +1917,16 @@
       <c r="G22" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22" t="str">
+        <f>_xlfn.XLOOKUP(A22,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>disruptive user</v>
+      </c>
+      <c r="I22" t="str">
+        <f>_xlfn.XLOOKUP(A22,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-07-28 09:56:11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>78</v>
       </c>
@@ -1394,8 +1948,16 @@
       <c r="G23" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H23" t="str">
+        <f>_xlfn.XLOOKUP(A23,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>FTU placed over 100 disruptive orders</v>
+      </c>
+      <c r="I23" t="str">
+        <f>_xlfn.XLOOKUP(A23,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-07 10:35:45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>81</v>
       </c>
@@ -1417,8 +1979,16 @@
       <c r="G24" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H24" t="e">
+        <f>_xlfn.XLOOKUP(A24,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I24" t="e">
+        <f>_xlfn.XLOOKUP(A24,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>85</v>
       </c>
@@ -1440,8 +2010,16 @@
       <c r="G25" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25" t="str">
+        <f>_xlfn.XLOOKUP(A25,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>FTU đặt hơn 100 đơn phá. Offensive user's name</v>
+      </c>
+      <c r="I25" t="str">
+        <f>_xlfn.XLOOKUP(A25,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-03 10:24:03</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>89</v>
       </c>
@@ -1463,8 +2041,16 @@
       <c r="G26" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H26" t="str">
+        <f>_xlfn.XLOOKUP(A26,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>disruptive user, TX Phạm Minh Truyền 2852976 báo cáo Kh 43138108 đặt phá đơn</v>
+      </c>
+      <c r="I26" t="str">
+        <f>_xlfn.XLOOKUP(A26,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-07-29 09:27:17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>92</v>
       </c>
@@ -1486,8 +2072,16 @@
       <c r="G27" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27" t="str">
+        <f>_xlfn.XLOOKUP(A27,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>FTU đặt hơn 200 đơn hàng, địa chỉ không cụ thể, các TX đều không liên hệ được</v>
+      </c>
+      <c r="I27" t="str">
+        <f>_xlfn.XLOOKUP(A27,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-07-24 10:24:04</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>96</v>
       </c>
@@ -1509,8 +2103,16 @@
       <c r="G28" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H28" t="str">
+        <f>_xlfn.XLOOKUP(A28,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>Fake orders. Đặt 61 đơn trong 3 ngày, không liên hệ được</v>
+      </c>
+      <c r="I28" t="str">
+        <f>_xlfn.XLOOKUP(A28,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-07-22 10:10:28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>100</v>
       </c>
@@ -1532,8 +2134,16 @@
       <c r="G29" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H29" t="e">
+        <f>_xlfn.XLOOKUP(A29,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I29" t="e">
+        <f>_xlfn.XLOOKUP(A29,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>103</v>
       </c>
@@ -1555,8 +2165,16 @@
       <c r="G30" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H30" t="str">
+        <f>_xlfn.XLOOKUP(A30,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>FTU đặt hơn 100 đơn phá, các TX đến nơi không liên hệ được</v>
+      </c>
+      <c r="I30" t="str">
+        <f>_xlfn.XLOOKUP(A30,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-07-23 11:30:19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>106</v>
       </c>
@@ -1578,8 +2196,16 @@
       <c r="G31" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H31" t="str">
+        <f>_xlfn.XLOOKUP(A31,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>FTU đặt hơn 40 đơn phá</v>
+      </c>
+      <c r="I31" t="str">
+        <f>_xlfn.XLOOKUP(A31,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-06 10:06:49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>109</v>
       </c>
@@ -1601,8 +2227,16 @@
       <c r="G32" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H32" t="e">
+        <f>_xlfn.XLOOKUP(A32,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I32" t="e">
+        <f>_xlfn.XLOOKUP(A32,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>112</v>
       </c>
@@ -1624,8 +2258,16 @@
       <c r="G33" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H33" t="e">
+        <f>_xlfn.XLOOKUP(A33,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I33" t="e">
+        <f>_xlfn.XLOOKUP(A33,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>115</v>
       </c>
@@ -1647,8 +2289,16 @@
       <c r="G34" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H34" t="str">
+        <f>_xlfn.XLOOKUP(A34,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>FTU placed over 100 disruptive order</v>
+      </c>
+      <c r="I34" t="str">
+        <f>_xlfn.XLOOKUP(A34,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-13 10:16:23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>118</v>
       </c>
@@ -1670,8 +2320,16 @@
       <c r="G35" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H35" t="str">
+        <f>_xlfn.XLOOKUP(A35,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>disruptive user, more than 20 fake orders</v>
+      </c>
+      <c r="I35" t="str">
+        <f>_xlfn.XLOOKUP(A35,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-17 08:56:05</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>121</v>
       </c>
@@ -1693,8 +2351,16 @@
       <c r="G36" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H36" t="str">
+        <f>_xlfn.XLOOKUP(A36,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>Fake order - Corp đặt 200 đơn phá, các TX đều ko liên hệ được</v>
+      </c>
+      <c r="I36" t="str">
+        <f>_xlfn.XLOOKUP(A36,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-07-22 10:25:04</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>125</v>
       </c>
@@ -1716,8 +2382,16 @@
       <c r="G37" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H37" t="e">
+        <f>_xlfn.XLOOKUP(A37,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I37" t="e">
+        <f>_xlfn.XLOOKUP(A37,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>128</v>
       </c>
@@ -1739,8 +2413,16 @@
       <c r="G38" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H38" t="e">
+        <f>_xlfn.XLOOKUP(A38,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I38" t="e">
+        <f>_xlfn.XLOOKUP(A38,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>134</v>
       </c>
@@ -1762,8 +2444,16 @@
       <c r="G39" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H39" t="e">
+        <f>_xlfn.XLOOKUP(A39,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I39" t="e">
+        <f>_xlfn.XLOOKUP(A39,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>138</v>
       </c>
@@ -1785,8 +2475,16 @@
       <c r="G40" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H40" t="str">
+        <f>_xlfn.XLOOKUP(A40,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>disruptive user</v>
+      </c>
+      <c r="I40" t="str">
+        <f>_xlfn.XLOOKUP(A40,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-14 09:43:19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>141</v>
       </c>
@@ -1808,8 +2506,16 @@
       <c r="G41" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H41" t="str">
+        <f>_xlfn.XLOOKUP(A41,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>FTU placed over 100 disruptive orders</v>
+      </c>
+      <c r="I41" t="str">
+        <f>_xlfn.XLOOKUP(A41,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-10 10:29:23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>144</v>
       </c>
@@ -1831,8 +2537,16 @@
       <c r="G42" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H42" t="str">
+        <f>_xlfn.XLOOKUP(A42,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>FTU placed over 100 disruptive order</v>
+      </c>
+      <c r="I42" t="str">
+        <f>_xlfn.XLOOKUP(A42,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-08-15 10:07:41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>147</v>
       </c>
@@ -1853,6 +2567,14 @@
       </c>
       <c r="G43" t="s">
         <v>12</v>
+      </c>
+      <c r="H43" t="str">
+        <f>_xlfn.XLOOKUP(A43,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$G$2:$G$33)</f>
+        <v>Disruptive user, TX Phạm Minh Truyền 2852976 báo cáo Kh 43166702 đặt phá</v>
+      </c>
+      <c r="I43" t="str">
+        <f>_xlfn.XLOOKUP(A43,'[1]Results export'!$F$2:$F$33,'[1]Results export'!$H$2:$H$33)</f>
+        <v>2031-07-30 10:00:09</v>
       </c>
     </row>
   </sheetData>
